--- a/artfynd/A 8545-2026 artfynd.xlsx
+++ b/artfynd/A 8545-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015448</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132015447</v>
       </c>
       <c r="B3" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,40 +925,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132015460</v>
+        <v>132015450</v>
       </c>
       <c r="B4" t="n">
-        <v>57906</v>
+        <v>92564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -968,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504919</v>
+        <v>504991</v>
       </c>
       <c r="R4" t="n">
-        <v>7001737</v>
+        <v>7001756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,17 +1005,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1055,39 +1050,40 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132015450</v>
+        <v>132015460</v>
       </c>
       <c r="B5" t="n">
-        <v>92563</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1097,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>504991</v>
+        <v>504919</v>
       </c>
       <c r="R5" t="n">
-        <v>7001756</v>
+        <v>7001737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,13 +1131,17 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>132015499</v>
       </c>
       <c r="B6" t="n">
-        <v>78280</v>
+        <v>78281</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>132015513</v>
       </c>
       <c r="B7" t="n">
-        <v>83114</v>
+        <v>83115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>132015514</v>
       </c>
       <c r="B8" t="n">
-        <v>83114</v>
+        <v>83115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>132015459</v>
       </c>
       <c r="B9" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>132015506</v>
       </c>
       <c r="B10" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>132015511</v>
       </c>
       <c r="B11" t="n">
-        <v>79268</v>
+        <v>79269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>132015458</v>
       </c>
       <c r="B12" t="n">
-        <v>57906</v>
+        <v>57907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,41 +2030,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132015451</v>
+        <v>132015516</v>
       </c>
       <c r="B13" t="n">
-        <v>92563</v>
+        <v>83241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2072,10 +2068,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504938</v>
+        <v>504954</v>
       </c>
       <c r="R13" t="n">
-        <v>7001764</v>
+        <v>7001715</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2127,17 +2123,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2155,40 +2151,39 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132015457</v>
+        <v>132015451</v>
       </c>
       <c r="B14" t="n">
-        <v>57906</v>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2198,10 +2193,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504998</v>
+        <v>504938</v>
       </c>
       <c r="R14" t="n">
-        <v>7001751</v>
+        <v>7001764</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2236,17 +2231,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2285,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132015516</v>
+        <v>132015508</v>
       </c>
       <c r="B15" t="n">
-        <v>83240</v>
+        <v>79269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2296,21 +2287,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2323,10 +2314,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504954</v>
+        <v>504928</v>
       </c>
       <c r="R15" t="n">
-        <v>7001715</v>
+        <v>7001731</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2378,17 +2369,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2406,10 +2397,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132015508</v>
+        <v>132015457</v>
       </c>
       <c r="B16" t="n">
-        <v>79268</v>
+        <v>57907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,26 +2408,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2444,10 +2440,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504928</v>
+        <v>504998</v>
       </c>
       <c r="R16" t="n">
-        <v>7001731</v>
+        <v>7001751</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2482,13 +2478,17 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>132015445</v>
       </c>
       <c r="B17" t="n">
-        <v>83248</v>
+        <v>83249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8545-2026 artfynd.xlsx
+++ b/artfynd/A 8545-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015448</v>
       </c>
       <c r="B2" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132015447</v>
       </c>
       <c r="B3" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>132015450</v>
       </c>
       <c r="B4" t="n">
-        <v>92564</v>
+        <v>92569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>132015460</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132015499</v>
       </c>
       <c r="B6" t="n">
-        <v>78281</v>
+        <v>78286</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>132015513</v>
       </c>
       <c r="B7" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>132015514</v>
       </c>
       <c r="B8" t="n">
-        <v>83115</v>
+        <v>83120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>132015459</v>
       </c>
       <c r="B9" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>132015506</v>
       </c>
       <c r="B10" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>132015511</v>
       </c>
       <c r="B11" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>132015458</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2030,37 +2030,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132015516</v>
+        <v>132015451</v>
       </c>
       <c r="B13" t="n">
-        <v>83241</v>
+        <v>92569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2068,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504954</v>
+        <v>504938</v>
       </c>
       <c r="R13" t="n">
-        <v>7001715</v>
+        <v>7001764</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,17 +2127,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2151,41 +2155,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132015451</v>
+        <v>132015508</v>
       </c>
       <c r="B14" t="n">
-        <v>92564</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504938</v>
+        <v>504928</v>
       </c>
       <c r="R14" t="n">
-        <v>7001764</v>
+        <v>7001731</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132015508</v>
+        <v>132015516</v>
       </c>
       <c r="B15" t="n">
-        <v>79269</v>
+        <v>83246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,21 +2287,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2314,10 +2314,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504928</v>
+        <v>504954</v>
       </c>
       <c r="R15" t="n">
-        <v>7001731</v>
+        <v>7001715</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,17 +2369,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2400,7 +2400,7 @@
         <v>132015457</v>
       </c>
       <c r="B16" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>132015445</v>
       </c>
       <c r="B17" t="n">
-        <v>83249</v>
+        <v>83254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 8545-2026 artfynd.xlsx
+++ b/artfynd/A 8545-2026 artfynd.xlsx
@@ -2276,10 +2276,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132015516</v>
+        <v>132015457</v>
       </c>
       <c r="B15" t="n">
-        <v>83246</v>
+        <v>57912</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,26 +2287,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2314,10 +2319,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504954</v>
+        <v>504998</v>
       </c>
       <c r="R15" t="n">
-        <v>7001715</v>
+        <v>7001751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2352,13 +2357,17 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2369,17 +2378,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2397,10 +2406,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132015457</v>
+        <v>132015516</v>
       </c>
       <c r="B16" t="n">
-        <v>57912</v>
+        <v>83246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,31 +2417,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2440,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504998</v>
+        <v>504954</v>
       </c>
       <c r="R16" t="n">
-        <v>7001751</v>
+        <v>7001715</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2478,17 +2482,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2499,17 +2499,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 8545-2026 artfynd.xlsx
+++ b/artfynd/A 8545-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132015448</v>
       </c>
       <c r="B2" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>132015447</v>
       </c>
       <c r="B3" t="n">
-        <v>91809</v>
+        <v>91811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>132015450</v>
       </c>
       <c r="B4" t="n">
-        <v>92569</v>
+        <v>92571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>132015460</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>132015499</v>
       </c>
       <c r="B6" t="n">
-        <v>78286</v>
+        <v>78288</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         <v>132015513</v>
       </c>
       <c r="B7" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>132015514</v>
       </c>
       <c r="B8" t="n">
-        <v>83120</v>
+        <v>83122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>132015459</v>
       </c>
       <c r="B9" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>132015506</v>
       </c>
       <c r="B10" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1779,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132015511</v>
+        <v>132015458</v>
       </c>
       <c r="B11" t="n">
-        <v>79274</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,26 +1790,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1817,10 +1822,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505021</v>
+        <v>504964</v>
       </c>
       <c r="R11" t="n">
-        <v>7001733</v>
+        <v>7001745</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1855,13 +1860,17 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1909,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132015458</v>
+        <v>132015511</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>79276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,31 +1920,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1943,10 +1947,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>504964</v>
+        <v>505021</v>
       </c>
       <c r="R12" t="n">
-        <v>7001745</v>
+        <v>7001733</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,17 +1985,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2030,39 +2030,40 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132015451</v>
+        <v>132015457</v>
       </c>
       <c r="B13" t="n">
-        <v>92569</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2072,10 +2073,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>504938</v>
+        <v>504998</v>
       </c>
       <c r="R13" t="n">
-        <v>7001764</v>
+        <v>7001751</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,13 +2111,17 @@
           <t>2026-03-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2160,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132015508</v>
+        <v>132015516</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>83248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,21 +2171,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2193,10 +2198,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>504928</v>
+        <v>504954</v>
       </c>
       <c r="R14" t="n">
-        <v>7001731</v>
+        <v>7001715</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2248,17 +2253,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2276,40 +2281,39 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132015457</v>
+        <v>132015451</v>
       </c>
       <c r="B15" t="n">
-        <v>57912</v>
+        <v>92571</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2319,10 +2323,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>504998</v>
+        <v>504938</v>
       </c>
       <c r="R15" t="n">
-        <v>7001751</v>
+        <v>7001764</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2357,17 +2361,13 @@
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132015516</v>
+        <v>132015508</v>
       </c>
       <c r="B16" t="n">
-        <v>83246</v>
+        <v>79276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>504954</v>
+        <v>504928</v>
       </c>
       <c r="R16" t="n">
-        <v>7001715</v>
+        <v>7001731</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2499,17 +2499,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2530,7 +2530,7 @@
         <v>132015445</v>
       </c>
       <c r="B17" t="n">
-        <v>83254</v>
+        <v>83256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
